--- a/data/trans_camb/IP19C07-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.2384182988121292</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.281668662153741</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.486301513536852</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.391992620644195</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.378283275188264</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-4.837042020494383</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-6.014010359483624</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-12.23973404792555</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.749576624512809</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-7.61075686835932</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.221388357310534</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-8.286776199280869</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>5.163001402798309</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-2.433188022827406</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.607153605588469</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.597932037004882</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>4.835406738588659</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-1.996782541523683</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.03331149263081818</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.8776665230442895</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.5096604261263166</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6953156707030327</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2296319041523658</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.8058859812250225</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5477040191726965</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3888322377764296</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3119183067294312</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.257256765835376</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-0.0516570412683726</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>3.121808524921513</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.601758851079108</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.183106951912705</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.2473283734344924</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.522410552246579</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.305122515677893</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6197035058960576</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.719631740686911</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.3366696145243792</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-3.054588925950624</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.024683891718853</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.568068475784347</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.656651509495498</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.166453957458023</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.707659113035987</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-6.795158883723563</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>5.423234909382789</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.778995296999548</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.699624345569836</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.248150365441084</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.467034250274268</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.371779427447599</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2171787135092993</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.471490594233141</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.07148980934234972</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3137402851093775</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.04312377348843671</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3912601412784856</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.7211349163479054</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.870325024113912</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.5150811134128529</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.7656175539438859</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4873959679916225</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6969821868760935</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.565307291055364</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.5680254193761984</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.478403480135383</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.8463764976703495</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7933339257934612</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.275106350758691</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-12.10681432139596</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-9.617122396109984</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-4.523405872505866</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.5784370811185463</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-8.416227699311515</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-4.856771987408126</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-19.42492699647295</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-18.25744641592018</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-12.17519058803489</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.982828976961645</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-13.41329149298537</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-10.11851790935062</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>-4.520798187368405</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-2.905922469661882</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.979370590717224</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.83380423153828</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-3.137886034338015</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.07542784450801363</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.7440916677574394</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.5910737914021124</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.464163083958833</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.05935552701119723</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.6421506738401602</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.3705673748177312</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.9476912476799201</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8106819336341448</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.8298928776211152</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.5032279987701475</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8203978848129709</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.5942877453913015</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>-0.343999146613819</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.2021434597652635</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.542914681039722</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1.409320186006128</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.2555443539243886</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.01229940265907824</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-7.422105028454165</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.5767283677712245</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-11.38380143318101</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-14.52480392746339</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-9.276362482135504</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-7.054478323241119</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-18.24862469902359</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-11.12686091269474</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-25.40245723995926</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-27.29508840256561</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-18.15586089071717</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-15.37922189690306</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>0.7683856023781923</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>9.060396431606128</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.779288393576952</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-2.559363737570702</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-1.340115854043202</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.5494387780917251</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.6413883107381988</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.04983853396596659</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4483889102766367</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.5721077482987372</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.5157030653842439</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3921813213949184</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.6374049979303447</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.7712050790152148</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.783468870434511</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.783129845192445</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6358197296008428</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.5201509823011119</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.692999435158359</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.2650620788718617</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.09731145247724382</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-0.07957284021540037</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.09139857923832798</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-4.151556102623266</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-3.69685874380427</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.348012093859823</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.51617417749452</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-2.761159858809235</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.691043114191144</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-7.296308804457306</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-6.899153589367837</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-4.500663013855927</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-5.370852920873698</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-5.189804852682978</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-5.107007430358066</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-0.7468793677515471</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-0.5115869418836851</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.17408913132714</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.12261567876678</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.4335618399280819</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.2947263211453524</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.4199099360394582</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.3739194847148694</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1403905321734324</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1579039984994425</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.2832626654426866</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.276069508585318</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6343229107258831</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.5970000170508266</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.4222052487716759</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.4560210126718298</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.4724807687819713</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.4590221767614661</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.08799550553681922</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.05152439263744703</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.2909017106199193</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.3067618852882954</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.04431062709892394</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.03285639124113597</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
